--- a/defis-mode-carriere.xlsx
+++ b/defis-mode-carriere.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Familles" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Défis'!$A$1:$U$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Familles'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Défis'!$A$1:$U$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Familles'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3003,8 +3003,393 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>La Révolution Digitale</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Le tournant du streaming</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Après 3 défis réussis</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Chaîne linéaire classique qui perd 1,5 point de PDA par saison, 25 M€ en caisse : il faut basculer une partie de la grille vers une plateforme FAST/AVOD maison</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Atteindre 500 000 utilisateurs actifs sur la plateforme et garder au moins 10 % de PDA en linéaire au bout de 5 saisons</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Chaque format exclusif au streaming coûte 0,5 point de PDA au linéaire mais augmente de 15 % la valorisation digitale ; si la trésorerie passe sous 0 M€, la plateforme est revendue au rabais</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Popularité digitale 20 · Crédibilité 60</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>ouverture de saison, début de saison, décision scénarisée, effet sur les jauges, après chaque décision, recettes pub par case, ligne de suivi, verdict de fin de saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Sous pression</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Le raider de la finance</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Après 5 défis réussis</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Un fonds activiste a racheté 40 % du capital et veut liquider le catalogue de fictions historiques pour se verser un dividende exceptionnel</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Garder le contrôle du conseil d'administration pendant 4 saisons et faire monter l'action de 30 %</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>À chaque début de saison, l'activiste soumet au vote une coupe de 15 M€ dans l'information ou la création : l'accepter fait monter l'action mais coûte 15 de moral et 20 de crédibilité, la refuser coûte 10 M€ de frais d'avocats</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Actionnaires 45 · Moral 60 · Crédibilité 60</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>ouverture de saison, décision scénarisée, effet sur les jauges, après chaque décision, recettes pub, ligne de suivi, verdict de fin de saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Destins de chaînes</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Fuite de cerveaux</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Dès le départ</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Après une dispute médiatique, vos trois animateurs vedettes du 19-23 h partent chez votre concurrent direct avec leurs équipes de production</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Renouveler entièrement la soirée (access et prime) et dépasser la PDA de votre rival en 3 saisons</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Interdiction de recruter des talents confirmés ou vedettes : seulement des espoirs. Les deux premières saisons, l'access perd 20 % de son audience</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Généraliste</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Nouveaux talents 15</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="n"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>début de saison, talents interdits, réaction aux signatures, effet sur les jauges, après chaque décision, ligne de suivi, verdict de fin de saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Ligne éditoriale</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>La chaîne Bas-Carbone</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Dès le départ</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>La direction s'engage à réduire de 60 % l'empreinte carbone des tournages et des retransmissions</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Atteindre 12 % de PDA avec un score éco-responsable au-dessus de 80, en 5 saisons au plus</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Tournages à l'étranger et formats d'aventure internationaux interdits ; la production locale coûte 15 % de plus la première saison</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Éco-responsable 50 · Crédibilité 70</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>programmes interdits, options interdites, effet sur les jauges, après chaque décision, réaction aux signatures, recettes pub, ligne de suivi, verdict de fin de saison</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Défis express</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Événement mondial</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Dès le départ</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Les droits exclusifs d'un événement sportif mondial pendant un mois : une seule saison intensive, de 7 % de PDA au sommet</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Générer au moins 50 M€ de recettes publicitaires nettes et atteindre un pic de 25 % de PDA pour la finale</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Garantie d'audience : à chaque décision, une case de grande écoute (access ou prime) sous 12 % de PDA coûte 3 M€ de remboursement aux annonceurs</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Attention médias 90</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="n"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>début de saison, recettes pub par case, effet sur les jauges, après chaque décision, audience de la finale, ligne de suivi, verdict de fin de saison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U34"/>
+  <autoFilter ref="A1:U39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3015,7 +3400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3164,10 +3549,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -3220,7 +3605,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3.2</v>
@@ -3248,10 +3633,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -3276,14 +3661,42 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>digital</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>La Révolution Digitale</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Le public a quitté le salon pour le smartphone. Plateformes, FAST, replay : inventez la télévision de demain sans perdre celle d'aujourd'hui.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>